--- a/Output.xlsx
+++ b/Output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
   <si>
     <t>topic</t>
   </si>
@@ -31,136 +31,187 @@
     <t>non_coding_projects</t>
   </si>
   <si>
+    <t>online_problem_sets</t>
+  </si>
+  <si>
     <t>video_resources</t>
   </si>
   <si>
     <t>text_resources</t>
   </si>
   <si>
-    <t>How to understand competitive programming problem statements more efficiently!</t>
-  </si>
-  <si>
-    <t>Basic programming knowledge including syntax, data types, and control structures; Familiarity with at least one programming language like C++, Java, or Python; Basic algorithmic thinking such as understanding loops and recursion; Exposure to simple data structures like arrays and lists; Prior attempts at solving competitive programming problems, even if unsuccessful.</t>
-  </si>
-  <si>
-    <t>Deconstructing the problem statement: Identifying key information, constraints, and the ultimate goal; Understanding input/output formats: How to correctly parse data and print results; Identifying edge cases and special conditions: Considering empty inputs, boundary values, and specific constraints; Formulating test cases: Creating manual tests and understanding the provided sample tests; Recognizing common problem patterns: Identifying known algorithms or data structures that might apply; Clarifying ambiguities: What to do if the problem isn't perfectly clear (though typically problems are well-defined in CP); Time and space complexity implications: How problem constraints guide the choice of algorithm and data structures.</t>
-  </si>
-  <si>
-    <t>Implement a robust parser that can handle various input formats (e.g., space-separated, comma-separated, multi-line structures) for competitive programming problems; Write a program to generate diverse test cases based on given problem constraints and examples; Solve a curated set of 'easy' competitive programming problems with the primary focus on accurate problem understanding, followed by a brute-force implementation; Refactor a solution to a previously misunderstood problem after gaining a clearer interpretation of its statement; Create a 'problem statement analyzer' tool that highlights keywords, numerical constraints, and potential data structures from a text input; Build a simple text-based adventure game where correctly interpreting instructions is key to progressing through levels.</t>
-  </si>
-  <si>
-    <t>Annotate five competitive programming problem statements from platforms like Codeforces or LeetCode, highlighting key phrases, constraints, examples, and implicit assumptions; Develop a detailed checklist for comprehensive problem statement analysis to be used before writing any code; Verbally 'walkthrough' five complex competitive programming problems, explaining your thought process for understanding each component and potential pitfalls; Participate in a 'mock interview' focused solely on articulating your understanding of a given problem statement and outlining an initial approach, without writing code; Summarize the core requirements and constraints of five challenging competitive programming problems into concise 1-2 sentence descriptions; Translate a competitive programming problem statement from one natural language to another to deepen comprehension and identify subtle nuances.</t>
-  </si>
-  <si>
-    <t>How to Read Competitive Programming Problems by William Fiset: https://www.youtube.com/watch?v=F0K4fR_mRkc; Competitive Programming: How To Read Problem Statements by Errichto: https://www.youtube.com/watch?v=jW01e6W44eE; Competitive Programming: Problem Solving Techniques (Part 1) by Topcoder (discusses problem analysis): https://www.youtube.com/watch?v=MInN51L6q7s; Competitive Programming - Understanding the Problem Statement by Codechef: https://www.youtube.com/watch?v=gS-22l8WJ5I; Competitive Programming Setup &amp; How To Start by NeetCode (mentions problem understanding as a key step): https://www.youtube.com/watch?v=c3_A8TfV670; How to think about competitive programming problems by Code with Alisha: https://www.youtube.com/watch?v=k_K8uWlqjG0</t>
-  </si>
-  <si>
-    <t>A Competitive Programmer's Guide to Problem Analysis on Topcoder: https://www.topcoder.com/thrive/articles/A%20Competitive%20Programmer's%20Guide%20to%20Problem%20Analysis; How to Approach a Competitive Programming Problem by GeeksforGeeks: https://www.geeksforgeeks.org/how-to-approach-a-competitive-programming-problem/; Competitive Programming 3 by Steven Halim and Felix Halim (refer to sections on problem parsing and strategy): https://cpbook.net/; Competitive Programming Handbook by Antti Laaksonen (check chapters on general problem-solving techniques and common pitfalls): https://cses.fi/book/book.pdf; The Art of Problem Solving forums and articles (search for discussions on competitive programming problem analysis and interpretation): https://artofproblemsolving.com/community; Problem Understanding Tips on Codeforces blogs (search for community-contributed blogs related to efficient problem interpretation): https://codeforces.com/blog/entry/78505</t>
-  </si>
-  <si>
-    <t>Touch Typing Accuracy Improvement</t>
-  </si>
-  <si>
-    <t>Basic understanding of keyboard layout (QWERTY, Dvorak, etc.);Familiarity with proper typing posture;Knowledge of touch typing basics (finger placement on home row, reaching keys without looking);Consistent practice habit;Patience and willingness to learn touch typing;Access to a computer and keyboard</t>
-  </si>
-  <si>
-    <t>Ergonomics and Posture for Typing;Home Row and Finger Placement Reinforcement;Common Error Patterns and Correction Techniques;Practice Drills for Accuracy vs. Speed;Advanced Typing Software and Websites for Feedback;Muscle Memory Development and Relaxation Techniques;Typing with Punctuation and Special Characters Accurately;Identifying and Fixing Personal Weak Spots in Typing</t>
-  </si>
-  <si>
-    <t>Build a simple Python script to calculate WPM and accuracy from user input;Develop a web-based typing test application with real-time feedback on errors;Create a personalized typing tutor that generates drills based on common mistakes identified from user input;Implement a text analysis tool to highlight frequently mistyped words from personal documents or generated texts;Design a game in a language like JavaScript or Python where correct typing clears obstacles or earns points;Write a program to visualize typing heatmaps showing finger usage and error hotspots;Develop a command-line typing practice tool focusing on specific character combinations</t>
-  </si>
-  <si>
-    <t>Keep a typing journal to track daily accuracy and WPM progress, noting specific error types;Practice transcribing audio into text accurately, focusing on maintaining rhythm and minimizing backspaces;Participate in online typing accuracy challenges and competitions to benchmark progress;Design a custom keyboard layout study plan to target specific error keys or difficult transitions;Create flashcards for difficult key combinations or common words you struggle with during practice;Record yourself typing and review the video to identify posture issues or inefficient finger movements;Practice 'mindful typing' by paying close attention to each key press and its corresponding finger</t>
-  </si>
-  <si>
-    <t>Learn Touch Typing in 15 Minutes - The Ultimate Guide to Touch Typing by Ratatype: https://www.youtube.com/watch?v=vv5Q8hWnJtY;How To Type Faster And More Accurately (Learn Touch Typing The Right Way) by Learn Lingo: https://www.youtube.com/watch?v=0wQv70T0gK4;Improve Your Typing Accuracy! (The SECRET To Typing FASTER and ACCURATELY) by TypeRacer: https://www.youtube.com/watch?v=q6bY2D4xXhA;The BEST Typing Practice For ACCURACY (Stop Making MISTAKES!) by Sean Type: https://www.youtube.com/watch?v=fM-I48K_3-w;Touch Typing - How To Type Faster And Accurately by Mike Locke: https://www.youtube.com/watch?v=Q-n_6g9aE-0;Advanced Touch Typing Tips For Speed &amp; Accuracy by Keybr: https://www.youtube.com/watch?v=gM8X0j2f3L8;Ergonomic Keyboard Typing Techniques to Prevent Injury by Ergonomics Health: https://www.youtube.com/watch?v=P2L-f9-81aQ</t>
-  </si>
-  <si>
-    <t>The Ultimate Guide to Touch Typing by Ratatype: https://www.ratatype.com/learn/;How to Learn Touch Typing: A Complete Guide by TypingClub Blog: https://www.typingclub.com/blog/how-to-learn-touch-typing/;Improve Your Typing Accuracy by Keybr Blog: https://www.keybr.com/blog/improve-typing-accuracy/;10 Tips to Improve Your Typing Speed and Accuracy by The TypingCat: https://thetypingcat.com/blog/10-tips-to-improve-your-typing-speed-and-accuracy;The Science Behind Typing: How to Increase Your Speed and Accuracy by Medium (LifeHack): https://medium.com/lifehack-tips/the-science-behind-typing-how-to-increase-your-speed-and-accuracy-4b5b7e3e8f5b;Touch Typing Made Easy by wikiHow: https://www.wikihow.com/Touch-Type;Best Online Typing Tutors for Speed and Accuracy by TechRadar: https://www.techradar.com/best/online-typing-tutors</t>
-  </si>
-  <si>
-    <t>R data.table module</t>
-  </si>
-  <si>
-    <t>Basic R programming knowledge (variables, data types, functions); Familiarity with R data frames; Understanding of basic data manipulation concepts (filtering, selecting, grouping, joining); Experience with installing and loading R packages; Basic understanding of vectorized operations in R.</t>
-  </si>
-  <si>
-    <t>Introduction to data.table: creating a data.table, basic structure, key differences from data.frame; Selecting rows and columns: `i` and `j` arguments, using expressions in `i` and `j`; Filtering and subsetting: conditional filtering, multiple conditions; Adding/updating/deleting columns: using `:=` operator, multiple assignments; Grouping and aggregation: `by` argument, multiple grouping columns, `.N`, `.SD`, `.BY`; Chaining operations: efficient method for sequential data manipulation; Joins (merges): `on` argument, `nomatch`, various join types (inner, left, right, full, cross); Reshaping data: `dcast` and `melt` from `data.table` for wide-to-long and long-to-wide transformations; Setting keys: `setkey` and `setDT` for performance optimization; Benchmarking and performance considerations: comparing `data.table` with `data.frame` and `dplyr`.</t>
-  </si>
-  <si>
-    <t>Data Cleaning and Exploration: Load a messy dataset (e.g., Kaggle Titanic dataset), clean missing values, convert data types, filter observations, calculate summary statistics (mean, median, count by group) using `data.table`.; Sales Data Analysis: Analyze a simulated sales dataset. Calculate total sales per product, sales per region, identify top 5 best-selling products, and find the average order value by customer segment using `data.table` aggregation and filtering.; Customer Churn Prediction Preprocessing: Preprocess a customer dataset for machine learning. Create new features (e.g., tenure, average monthly charges), handle categorical variables, and perform train/test split, all using `data.table` operations.; Website Traffic Analysis: Analyze web server logs. Count unique visitors per day, identify most visited pages, track user sessions, and perform time-based aggregations using `data.table` with date/time manipulations.; Financial Data Aggregation: Aggregate stock market data. Calculate daily returns, moving averages (e.g., 5-day, 20-day), and identify periods of high volatility for multiple stocks using `data.table` by-group operations and rolling window calculations.</t>
-  </si>
-  <si>
-    <t>Conceptual Comparison: Write a detailed report comparing `data.table` with base R data frames and `dplyr` for common data manipulation tasks. Focus on syntax, performance, and use cases.; Cheat Sheet Creation: Design a comprehensive `data.table` cheat sheet covering common operations (selection, filtering, aggregation, joins, reshaping) with clear examples and syntax explanations.; Performance Analysis Plan: Develop a plan to benchmark `data.table` operations against `dplyr` on large datasets. Outline the metrics to track, the specific operations to test, and how to interpret the results.; Use Case Identification: Research and document five real-world scenarios where `data.table`'s speed and concise syntax would be particularly advantageous over other R packages or methods.; Tutorial Outline: Create a detailed outline for a beginner-friendly tutorial on 'Getting Started with R data.table'. Include learning objectives, topics to cover, and examples for each section.</t>
-  </si>
-  <si>
-    <t>An Introduction to data.table: 'R data.table Tutorial for Beginners' by DataCamp: https://www.youtube.com/watch?v=s5R7tNq6G4Q; Advanced data.table Techniques: 'Advanced R data.table Techniques' by DataCamp: https://www.youtube.com/watch?v=J_SjW0wF6H0; data.table vs. dplyr: 'R data.table vs dplyr: What's the Best Way to Manipulate Data in R?' by Code With Coder: https://www.youtube.com/watch?v=cK_YV8XQ0k8; data.table Joins: 'R data.table merge / join Explained with Examples' by The R Data Guru: https://www.youtube.com/watch?v=Tq_Yc2b_h40; Efficient Data Manipulation with data.table: 'Efficient Data Wrangling with data.table in R' by RStudio Webinars: https://www.youtube.com/watch?v=gYw4e9p7YFk</t>
-  </si>
-  <si>
-    <t>Official data.table Wiki/Documentation: 'data.table Introduction Vignette': https://rdatatable.gitlab.io/data.table/articles/datatable-intro.html; R data.table Official Website: 'data.table main page and documentation': https://rdatatable.github.io/data.table/; DataCamp Tutorial: 'Data Manipulation with data.table in R': https://www.datacamp.com/tutorial/data-manipulation-data-table-r; Analytics Vidhya Article: 'A Comprehensive Guide to data.table in R (for beginners)': https://www.analyticsvidhya.com/blog/2016/03/comprehensive-guide-data-table-r-beginners/; Stack Overflow data.table Tag Wiki: 'data.table - Tag Wiki': https://stackoverflow.com/tags/r-datatable/info</t>
-  </si>
-  <si>
-    <t>Excel Pivot Tables</t>
-  </si>
-  <si>
-    <t>Basic understanding of Microsoft Excel interface and navigation; Familiarity with basic Excel formulas and functions (SUM, AVERAGE, COUNT); Knowledge of data types and how to organize data in tabular format; Ability to work with ranges and cells in Excel; Understanding of basic data analysis concepts.</t>
-  </si>
-  <si>
-    <t>Introduction to Pivot Tables: What they are and why they are used; Creating a Pivot Table: From a data range or external data source; Understanding Pivot Table Fields: Rows, Columns, Values, Filters; Manipulating Pivot Table Layout: Changing field positions, collapsing/expanding items; Summarizing Data: SUM, COUNT, AVERAGE, MAX, MIN, Product, StdDev, Var; Grouping Data: By dates, numbers, and custom groups; Filtering and Sorting: Using Slicers and Timelines for interactive filtering; Calculated Fields and Items: Creating custom calculations within the pivot table; Pivot Charts: Visualizing pivot table data; Refreshing and Modifying Pivot Tables: Updating data and changing source; Advanced Pivot Table Options: Show Values As (e.g., % of Grand Total, Rank), Drill Down.</t>
-  </si>
-  <si>
-    <t>Automate Pivot Table Creation: Write a VBA macro to automatically create a pivot table from a selected data range, defining specific fields for rows, columns, and values; Dynamic Pivot Table Filtering: Develop a VBA script to change pivot table filters based on user input or a cell value; Refresh All Pivot Tables: Create a macro to refresh all pivot tables in a workbook with a single click; Pivot Table Report Generation: Write VBA code to iterate through a list of values in a filter field, create a separate sheet for each filtered view, and copy the pivot table data; Conditional Formatting based on Pivot Table Values: Implement a macro to apply specific conditional formatting rules to a pivot table's value area based on thresholds.</t>
-  </si>
-  <si>
-    <t>Sales Data Analysis: Analyze a dataset of sales transactions to identify top-selling products, regions, and salespersons using pivot tables; Customer Demographics Report: Create a pivot table to summarize customer data (age, gender, location) to understand customer segments; Expense Tracking Dashboard: Develop a pivot table-based dashboard to track and categorize personal or business expenses over time; HR Employee Data Analysis: Use pivot tables to analyze employee data such as department distribution, average salaries by role, and tenure; Inventory Management Report: Build a pivot table to summarize inventory levels, identify slow-moving items, and track stock valuation; Website Analytics Summary: Analyze website traffic data (e.g., page views, unique visitors, referral sources) using pivot tables to identify trends and popular content.</t>
-  </si>
-  <si>
-    <t>Excel Pivot Tables Tutorial for Beginners by Leila Gharani - https://www.youtube.com/watch?v=s_e_YhC2D8Y; Excel Pivot Tables: The Basics by Simon Sez IT - https://www.youtube.com/watch?v=JmKx-qFvB24; Advanced Excel Pivot Tables Tutorial by Excel Campus - Jon - https://www.youtube.com/watch?v=6rL0iYV19oI; How to Use Slicers in Excel by MyOnlineTrainingHub - https://www.youtube.com/watch?v=yYvT7D2t2G0; Calculated Fields &amp; Items in Excel Pivot Tables by ExcelIsFun - https://www.youtube.com/watch?v=0kI60rUfLzE; Pivot Charts in Excel by Kevin Stratvert - https://www.youtube.com/watch?v=h9gU7K13R7U.</t>
-  </si>
-  <si>
-    <t>Microsoft Support: Create a PivotTable to analyze worksheet data - https://support.microsoft.com/en-us/office/create-a-pivottable-to-analyze-worksheet-data-a9a84538-bfe9-40a9-a8e9-f99134456576; Exceljet: Excel Pivot Tables tutorial - https://exceljet.net/excel-pivot-tables-tutorial; Contextures: Excel Pivot Tables - https://www.contextures.com/excel-pivot-table.html; Investopedia: Pivot Table - https://www.investopedia.com/terms/p/pivot-table.asp; HubSpot: The Ultimate Guide to Excel Pivot Tables - https://blog.hubspot.com/marketing/excel-pivot-tables; Chandoo.org: Introduction to Pivot Tables - https://chandoo.org/wp/excel-pivot-tables-introduction/.</t>
-  </si>
-  <si>
-    <t>Drunkard's Walk Problem</t>
-  </si>
-  <si>
-    <t>Basic probability theory, including concepts like independent events, conditional probability, and expected value; Understanding of discrete random variables and their distributions (e.g., Bernoulli, Binomial); Fundamental calculus for continuous aspects or limiting behaviors; Basic understanding of algorithms and programming logic, ideally in Python for simulation; Familiarity with basic statistical concepts like mean and variance.</t>
-  </si>
-  <si>
-    <t>One-Dimensional Random Walks: definitions, probability of returning to origin, hitting times, absorption probabilities; Two-Dimensional Random Walks: recurrence vs. transience, path visualization, and properties; Higher-Dimensional Random Walks: general properties and comparisons to 1D and 2D; Biased Random Walks: introducing a preferred direction, analyzing drift and long-term behavior; Connection to Brownian Motion: how discrete random walks approximate continuous diffusion processes; Random Walks on Graphs: exploring state transitions on networks and their applications in graph theory; Self-Avoiding Walks: definition and challenges in analysis due to non-Markovian property; Applications of Random Walks: in statistical physics, finance (modeling stock prices), biology (molecular diffusion), and computer science (randomized algorithms).</t>
-  </si>
-  <si>
-    <t>1D Random Walk Simulator: Write a Python program to simulate a 1D random walk, plot the position over time, and calculate the final displacement and number of steps to return to origin; 2D Random Walk Visualizer: Develop a Python simulation to visualize a drunkard's path on a 2D grid, showing the path and end point, and check if it returns to a specific region; Absorption Probability Calculator: Implement a simulation to estimate the probability of a 1D random walk reaching one boundary before another, given starting position and step probabilities; Biased Random Walk Analysis: Simulate a 1D or 2D biased random walk and analyze how the bias affects the average displacement and path characteristics; Random Walk on a Grid/Maze: Implement a random walk algorithm to explore a given grid or maze, perhaps to find a target or calculate the average exploration time.</t>
-  </si>
-  <si>
-    <t>Conceptual Analysis of Recurrence and Transience: Research and explain the difference between recurrent and transient random walks, providing intuitive explanations and examples for 1D, 2D, and 3D cases; Mathematical Derivation of 1D Return Probability: Derive the probability that a 1D symmetric random walk returns to its origin at some point, and discuss the implications; Problem Solving with Expected Values: Given a scenario of a 1D random walk with specific boundaries, calculate the expected number of steps to reach a boundary using probability arguments; Literature Review of Random Walk Applications: Research and summarize three distinct real-world applications of random walks, detailing how the model is used and its limitations; Historical Overview of Random Walks: Create a presentation or report on the historical development of random walk theory, highlighting key mathematicians and their contributions.</t>
-  </si>
-  <si>
-    <t>StatQuest with Josh Starmer: Random Walk - Introduction to 1D and 2D random walks with clear explanations. https://www.youtube.com/watch?v=O11X4gGqF9g; MIT 18.05 Introduction to Probability and Statistics: Random Walks - A lecture covering the mathematical foundations and properties of random walks. https://www.youtube.com/watch?v=s5R5tG0i0gQ; 3Blue1Brown: Brownian motion and its random walk origins - A visually intuitive explanation connecting random walks to continuous processes. https://www.youtube.com/watch?v=stxYq2728rA; Khan Academy: Random Walks - A series of videos introducing the concept of random walks and related probability. https://www.khanacademy.org/science/ap-statistics/probability-ap/random-variables-discrete/v/random-walks; Professor Leonard: The Drunkard's Walk - Probability and Random Variables - A detailed lecture on the problem within the context of probability theory. https://www.youtube.com/watch?v=Vl03pXb66v8</t>
-  </si>
-  <si>
-    <t>Wikipedia: Random walk - Comprehensive overview with definitions, properties, and applications across dimensions. https://en.wikipedia.org/wiki/Random_walk; A First Course in Probability by Sheldon Ross: Chapter on Random Walks - Provides a rigorous mathematical treatment of discrete random walks. (Refer to the textbook, specific chapter varies by edition) https://www.pearson.com/us/higher-education/product/Ross-First-Course-in-Probability-A-10th-Edition/9780134997561.html; The Drunkard's Walk: How Randomness Rules Our Lives by Leonard Mlodinow - A popular science book offering an accessible and engaging introduction to randomness, including random walks. https://www.penguinrandomhouse.com/books/142945/the-drunkards-walk-by-leonard-mlodinow/; Brilliant.org: Random Walk - Interactive lessons and problems to build an intuitive and mathematical understanding. https://brilliant.org/wiki/random-walk/; Introduction to Probability by D.P. Bertsekas and J.N. Tsitsiklis: Sections on Discrete-Time Markov Chains and Random Walks - Provides an excellent academic foundation. (Refer to the textbook, usually in chapters related to Markov Chains) https://www.athenasc.com/probbook.html; Probability and Random Processes by Geoffrey Grimmett and David Stirzaker: Dedicated sections on Random Walks - An advanced textbook for deeper mathematical understanding. https://www.cambridge.org/core/books/probability-and-random-processes/D9A95C553BA653E1CC733E9A403F5927</t>
-  </si>
-  <si>
-    <t>Linear Recurrence Relations (1st and 2nd Order)</t>
-  </si>
-  <si>
-    <t>Basic Algebra (solving linear equations, polynomials); Sequences and Series (understanding arithmetic and geometric progressions, summation notation); Mathematical Induction (for proving closed-form solutions); Functions and their notation (understanding f(n) vs f(n-1)); Complex Numbers (for solving characteristic equations with complex roots in 2nd order relations); Differential Equations (conceptual similarity to solving linear homogeneous DEs may be helpful but not strictly required)</t>
-  </si>
-  <si>
-    <t>Definition and types of recurrence relations; Solving 1st-order homogeneous linear recurrence relations with constant coefficients (e.g., an = ran-1); Solving 1st-order non-homogeneous linear recurrence relations (e.g., an = ran-1 + f(n)) using method of undetermined coefficients; Definition of 2nd-order linear recurrence relations (e.g., an = ran-1 + san-2); Solving 2nd-order homogeneous linear recurrence relations by finding the characteristic equation (distinct real roots, repeated real roots, complex conjugate roots); Solving 2nd-order non-homogeneous linear recurrence relations using the method of undetermined coefficients for common f(n) types; Applications of recurrence relations (e.g., Fibonacci sequence, Tower of Hanoi, compound interest, population growth models); Generating functions for solving recurrence relations (an advanced technique)</t>
-  </si>
-  <si>
-    <t>Implement a Python function to solve and generate terms for any 1st-order linear homogeneous recurrence relation given initial conditions and the constant factor; Write a program in Java or C++ to calculate the nth term of the Fibonacci sequence using both recursive and iterative approaches, and compare their performance; Develop a C# application that takes coefficients and initial conditions for a 2nd-order homogeneous linear recurrence relation and outputs the first 'k' terms and the general closed-form solution, handling distinct, repeated, and complex roots; Create a JavaScript web tool that simulates the Tower of Hanoi problem, showing the moves and verifying the number of steps follows the appropriate recurrence relation; Build a small data visualization project in Python using Matplotlib to plot the terms of a population growth model defined by a 1st-order non-homogeneous recurrence relation over time; Design a solver in R for common 2nd-order non-homogeneous linear recurrence relations, allowing users to input the homogeneous part coefficients, initial conditions, and the form of the non-homogeneous term.</t>
-  </si>
-  <si>
-    <t>Derive the closed-form solution for at least three different 1st-order linear recurrence relations (e.g., compound interest, population growth) and prove them using mathematical induction; Analyze the behavior of 2nd-order homogeneous recurrence relations with different types of characteristic roots (e.g., two distinct real roots, a repeated real root, complex conjugate roots), explaining how the roots influence the sequence's growth or oscillation; Research and present on three real-world applications of linear recurrence relations outside of typical examples, such as in algorithm analysis (e.g., merge sort complexity), economics, or physics; Solve a set of five challenging 2nd-order non-homogeneous linear recurrence problems by hand, detailing each step of finding both the homogeneous and particular solutions; Create a comprehensive study guide or flowchart illustrating the entire process of solving 1st and 2nd-order linear recurrence relations, covering all cases for homogeneous and non-homogeneous types; Develop a series of word problems that can be modeled by 1st or 2nd-order linear recurrence relations, providing step-by-step solutions for each.</t>
-  </si>
-  <si>
-    <t>MIT OpenCourseWare: Mathematics for Computer Science - Recurrence Relations (Lecture 17): https://www.youtube.com/watch?v=F3zWvGkX_rY; Khan Academy: Recurrence relation introduction (Discrete mathematics): https://www.youtube.com/watch?v=R9K1o4Lw14g; The Organic Chemistry Tutor: Solving Recurrence Relations - Discrete Mathematics: https://www.youtube.com/watch?v=J_jKjT41eU4; Kimberly Brehm: Solving Linear Homogeneous Recurrence Relations with Constant Coefficients (covers various root types, playlist often linked): https://www.youtube.com/watch?v=Yf1e5-V8l2k; PatrickJMT: Second Order Linear Recurrence Relations - Distinct Real Roots: https://www.youtube.com/watch?v=s4H9rW2L04Q; Neso Academy: Recurrence Relation | Discrete Mathematics | First Order, Second Order, Homogeneous, Non Homogeneous: https://www.youtube.com/watch?v=nE5n3-1k6m0</t>
-  </si>
-  <si>
-    <t>Brilliant.org: Linear Recurrence Relations (multiple articles with examples and problems): https://brilliant.org/wiki/linear-recurrence-relations/; Tutorials Point: Discrete Mathematics - Recurrence Relation (a good overview with solved examples): https://www.tutorialspoint.com/discrete_mathematics/discrete_mathematics_recurrence_relation.htm; Wikipedia: Linear recurrence with constant coefficients (detailed theoretical explanation with examples): https://en.wikipedia.org/wiki/Linear_recurrence_with_constant_coefficients; Lumen Learning: Discrete Mathematics - Recurrence Relations (interactive examples and practice): https://courses.lumenlearning.com/suny-albany-discrete-mathematics/chapter/recurrence-relations/; GeeksforGeeks: Recurrence Relations (articles often include common problems and algorithmic applications): https://www.geeksforgeeks.org/recurrence-relations/; Discrete Mathematics and Its Applications by Kenneth H. Rosen (Chapter 7: Recurrence Relations - widely used textbook for comprehensive coverage): https://www.amazon.com/Discrete-Mathematics-Applications-Kenneth-Rosen/dp/0073383090</t>
+    <t>Surds</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of square roots and cube roots; Concept of prime factorization; Basic algebraic manipulation; Knowledge of number types (integers, rational numbers).</t>
+  </si>
+  <si>
+    <t>Definition of a surd; Simplifying surds; Adding and subtracting surds; Multiplying surds; Dividing surds and rationalizing the denominator; Conjugate surds; Solving equations involving surds; Real-world applications of surds; Operations with higher order roots; Comparison of surds.</t>
+  </si>
+  <si>
+    <t>Python script to simplify surds; Java program to perform arithmetic operations on surds (add, subtract, multiply, divide); C++ function to rationalize a surd denominator; Web application (e.g., using JavaScript) for a surd calculator; Algorithm to identify if a number is a perfect square/cube/etc. for surd simplification; Interactive surd quiz generator in Python.</t>
+  </si>
+  <si>
+    <t>Create a step-by-step guide on simplifying surds using different examples; Develop a set of flashcards for surd rules and definitions; Design a poster explaining the process of rationalizing the denominator; Create a real-world problem scenario where surds are used (e.g., calculating diagonal of a square with irrational sides); Prepare a presentation on the history and importance of irrational numbers and surds; Build a flowchart for solving surd equations.</t>
+  </si>
+  <si>
+    <t>Khan Academy Surds Practice: https://www.khanacademy.org/math/algebra/rational-and-irrational-numbers/simplifying-surds/e/simplifying-surds; Corbettmaths Surds Worksheets: https://corbettmaths.com/contents/ (search for surds); Math-Drills Surds Worksheets: https://www.math-drills.com/algebra/algebra_simplifying_radicals.php; BBC Bitesize Surds Quizzes: https://www.bbc.co.uk/bitesize/guides/zc2g8xs/revision/1; Dr. Frost Maths Surds Practice: https://www.drfrostmaths.com/resources/ (search for surds).</t>
+  </si>
+  <si>
+    <t>Khan Academy - Introduction to Surds: https://www.khanacademy.org/math/algebra/rational-and-irrational-numbers/simplifying-surds/v/understanding-irrational-numbers-as-surds; Eddie Woo - Simplifying Surds: https://www.youtube.com/watch?v=3g3o_pM5bLg; The Organic Chemistry Tutor - Surds Basic Introduction: https://www.youtube.com/watch?v=68e1Q6oD8L0; Maths Made Easy - Rationalising the Denominator: https://www.youtube.com/watch?v=1F566lJ9X3s; ExamSolutions - Full Surds Playlist: https://www.youtube.com/playlist?list=PLBEEAC6F5B468F6C2; Khan Academy - Adding and Subtracting Surds: https://www.youtube.com/watch?v=x02x58Hq-1A.</t>
+  </si>
+  <si>
+    <t>GCSE Maths Textbook (e.g., Edexcel, AQA) Surds Chapter; Maths is Fun - Surds: https://www.mathsisfun.com/surds.html; BBC Bitesize - Surds Revision: https://www.bbc.co.uk/bitesize/guides/zc2g8xs/revision/1; Wikipedia - Nth Root (covers surds): https://en.wikipedia.org/wiki/Nth_root; Plus magazine - The power of Surds: https://plus.maths.org/content/power-surds; Schaum's Outline of College Algebra (relevant chapters).</t>
+  </si>
+  <si>
+    <t>Exponents</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of multiplication as repeated addition; Concept of positive and negative numbers; Basic algebraic expressions; Factorization.</t>
+  </si>
+  <si>
+    <t>Definition of exponents (powers/indices); Rules of exponents (product rule, quotient rule, power rule); Zero exponent rule; Negative exponent rule; Fractional exponents (roots); Solving exponential equations; Scientific notation; Exponential growth and decay; Operations with different bases; Laws of indices in algebra.</t>
+  </si>
+  <si>
+    <t>Python function to calculate powers (e.g., x^y); JavaScript program to convert numbers to scientific notation and vice versa; C++ program demonstrating exponential growth/decay scenarios; Web-based calculator for applying exponent rules; Python script to solve simple exponential equations (e.g., 2^x = 8); Interactive quiz on exponent rules in a chosen language.</t>
+  </si>
+  <si>
+    <t>Create a poster summarizing all exponent rules with examples; Develop a board game where players apply exponent rules to advance; Research and present on real-world applications of exponential growth (e.g., population growth, compound interest); Design a flowchart for simplifying expressions with multiple exponent rules; Write a short story or scenario involving a concept of exponential decay (e.g., radioactive decay); Prepare a presentation on the history of exponents and their notation.</t>
+  </si>
+  <si>
+    <t>Khan Academy Exponents Practice: https://www.khanacademy.org/math/algebra/rational-and-irrational-numbers/exponent-properties/e/exponent-properties-1; Corbettmaths Exponents Worksheets: https://corbettmaths.com/contents/ (search for indices); Math-Drills Exponents Worksheets: https://www.math-drills.com/algebra/algebra_exponents.php; IXL Math - Exponents: https://www.ixl.com/math/grade-8/properties-of-exponents; Dr. Frost Maths Indices Practice: https://www.drfrostmaths.com/resources/ (search for indices).</t>
+  </si>
+  <si>
+    <t>Khan Academy - Exponent Rules Review: https://www.khanacademy.org/math/algebra/rational-and-irrational-numbers/exponent-properties/v/exponent-rules-review; The Organic Chemistry Tutor - Basic Exponents Rules: https://www.youtube.com/watch?v=gq83LpNTJ7E; Eddie Woo - Introduction to Indices (Exponents): https://www.youtube.com/watch?v=e_04r7-V824; Maths Made Easy - All Indices Rules Explained: https://www.youtube.com/watch?v=vV_Xy2r8-3g; ExamSolutions - Indices and Laws of Indices Playlist: https://www.youtube.com/playlist?list=PLBEEAC6F5B468F6C2; Professor Dave Explains - Exponent Rules: https://www.youtube.com/watch?v=Zf_z480I80k.</t>
+  </si>
+  <si>
+    <t>GCSE Maths Textbook (e.g., Edexcel, AQA) Indices Chapter; Maths is Fun - Exponents: https://www.mathsisfun.com/exponent.html; BBC Bitesize - Laws of Indices: https://www.bbc.co.uk/bitesize/guides/zc2g8xs/revision/2; Wikipedia - Exponentiation: https://en.wikipedia.org/wiki/Exponentiation; Purplemath - Exponents and Radicals: https://www.purplemath.com/modules/exponent.htm; Schaum's Outline of College Algebra (relevant chapters).</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of square roots and cube roots; Familiarity with prime factorization; Knowledge of basic algebraic manipulation; Understanding of inverse operations.</t>
+  </si>
+  <si>
+    <t>Definition of a surd and radical notation; Simplifying surds by extracting perfect square factors; Addition and subtraction of surds with like and unlike terms; Multiplication of surds (monomial by monomial, monomial by binomial, binomial by binomial); Division of surds and rationalizing the denominator (single term surd); Rationalizing the denominator with binomial surds using conjugates; Solving simple equations involving surds and checking for extraneous solutions; Applications of surds in geometry (Pythagorean theorem, area calculations); Converting between entire surds and mixed surds.</t>
+  </si>
+  <si>
+    <t>Surd Simplifier: A Python program that takes an integer and returns its simplest surd form, e.g., sqrt(72) -&gt; 6sqrt(2); Surd Arithmetic Calculator: Develop a console application that allows users to input two surds and an operation (add, subtract, multiply, divide) and outputs the simplified result; Rationalize Denominator Tool: Create a web-based utility using JavaScript that takes an expression like 1/(sqrt(3)-sqrt(2)) and returns the rationalized form; Surd Equation Solver (basic): Implement a script to solve simple linear equations involving a single surd, such as 2 + sqrt(x) = 5; Interactive Surd Quiz Generator: Build a program that generates random surd simplification or operation questions and checks user answers.</t>
+  </si>
+  <si>
+    <t>Surd Puzzle Book: Compile a collection of crossword puzzles, number searches, and matching games based on surd simplification and operations; Geometric Application of Surds: Design a poster or presentation demonstrating how surds arise naturally in the dimensions of regular polygons or 3D shapes (e.g., diagonal of a cube); Surd Card Game: Create a card game where players match unsimplified surd expressions with their simplified counterparts or perform operations to win; Historical Exploration of Irrationals: Research and present on the discovery of irrational numbers and the development of surd notation throughout history; Surd-Based Art Project: Create a visual art piece where different colours or patterns correspond to simplified surd values or relationships.</t>
+  </si>
+  <si>
+    <t>Khan Academy - Simplifying Square Roots: https://www.khanacademy.org/math/algebra/rational-exponents-and-radicals/simplifying-radicals/e/simplifying_radicals; DrFrostMaths - Surds Worksheets (requires login for solutions): https://www.drfrostmaths.com/resources/resource.php?rid=363; Corbettmaths - Surds Practice Questions and Solutions: https://corbettmaths.com/2013/05/29/surds/; Maths Genie - Surds Problems and worked solutions: https://www.mathsgenie.co.uk/surds.html; ExamSolutions - Surds Core Maths Tutorials and Exercises: https://www.examsolutions.net/a-level-maths/core-maths/surds/</t>
+  </si>
+  <si>
+    <t>Khan Academy - Simplifying Square Roots (video tutorial): https://www.youtube.com/watch?v=sOQJk2x-gS0; The Organic Chemistry Tutor - Adding, Subtracting, Multiplying, Dividing Radicals: https://www.youtube.com/watch?v=GjY6K1W_M6g; Maths Genie - Rationalising the Denominator with worked examples: https://www.youtube.com/watch?v=s_e5vY-y920; ExamSolutions - Surds - Introduction and Simplification Explained: https://www.youtube.com/watch?v=S0y_oR662-o; Eddie Woo - Introduction to Surds (detailed explanation): https://www.youtube.com/watch?v=F3zWwN1qS4g</t>
+  </si>
+  <si>
+    <t>BBC Bitesize - Surds Explained with examples and quizzes: https://www.bbc.co.uk/bitesize/guides/zp6gfg8/revision/1; Maths Is Fun - Surds Introduction and Examples: https://www.mathsisfun.com/surds.html; Paul's Online Math Notes - Radicals and Rational Exponents (comprehensive guide): https://tutorial.math.lamar.edu/Classes/Alg/Radicals.aspx; CK-12 Foundation - Simplifying Radicals (textbook content with exercises): https://www.ck12.org/algebra/simplifying-radicals-algebra/lesson/Simplifying-Radicals/; Higher Maths - Surds (Scottish curriculum focused, but broadly applicable): https://www.highermaths.co.uk/surds/</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of multiplication as repeated addition; Familiarity with prime factorization; Basic understanding of algebraic expressions.</t>
+  </si>
+  <si>
+    <t>Definition of exponents (powers, indices) and basic terminology (base, exponent); Laws of exponents for multiplication (x^a * x^b = x^(a+b)); Laws of exponents for division (x^a / x^b = x^(a-b)); Power of a power law ((x^a)^b = x^(a*b)); Power of a product and quotient laws ((xy)^a = x^a y^a, (x/y)^a = x^a / y^a); Zero exponent (x^0 = 1); Negative exponents (x^-a = 1/x^a); Rational (fractional) exponents (x^(1/n) = nth root of x, x^(m/n) = (nth root of x)^m); Scientific notation and its application; Solving simple exponential equations.</t>
+  </si>
+  <si>
+    <t>Exponent Calculator: Build a Python program that takes a base and exponent and calculates the result, including negative and fractional exponents; Scientific Notation Converter: Develop a C# or Java application that converts numbers between standard decimal form and scientific notation; Exponential Growth/Decay Simulator: Create a simulation using any programming language to model population growth, compound interest, or radioactive decay over time; Laws of Exponents Quiz Game: Design an interactive quiz in HTML/CSS/JavaScript where users simplify expressions using exponent rules; Base Converter: Implement a tool that converts numbers between different integer bases (e.g., decimal to binary, binary to hexadecimal) demonstrating powers of the base.</t>
+  </si>
+  <si>
+    <t>Laws of Exponents Infographic: Design a visually appealing poster or digital infographic summarizing all the laws of exponents with clear examples; Exponential Growth Model with Paper Folding: Use a physical demonstration with paper folding to illustrate how thickness or area grows exponentially; Historical Timeline of Exponents: Research and create a timeline showcasing the evolution of exponential notation and its key contributors; Exponent Bingo Game: Develop a bingo game where cards have simplified exponent expressions and the caller reads out unsimplified ones; Financial Literacy Project: Create a presentation or report illustrating the power of compound interest for savings and investments using real-world scenarios.</t>
+  </si>
+  <si>
+    <t>Khan Academy - Exponent Rules (review and practice): https://www.khanacademy.org/math/algebra/rational-exponents-and-radicals/exponent-properties-review/e/exponent_rules_1; IXL Math - Exponents and Powers (interactive exercises by grade level): https://www.ixl.com/math/grade-8/evaluate-expressions-using-properties-of-exponents; Corbettmaths - Indices Introduction and practice questions: https://corbettmaths.com/2013/05/17/indices-introduction/; DrFrostMaths - Indices Worksheets and topic tests (requires login for solutions): https://www.drfrostmaths.com/resources/resource.php?rid=361; Maths Genie - Indices Problems (including negative and fractional powers): https://www.mathsgenie.co.uk/indices.html</t>
+  </si>
+  <si>
+    <t>Khan Academy - Exponent Rules (comprehensive video lesson): https://www.youtube.com/watch?v=gS6v-j59l9A; The Organic Chemistry Tutor - Basic Exponent Rules &amp; Properties: https://www.youtube.com/watch?v=Xw0lG9bKk7Y; Professor Dave Explains - Laws of Exponents Made Easy: https://www.youtube.com/watch?v=kYv_v4nS9Xw; Eddie Woo - Introduction to Indices and why they are useful: https://www.youtube.com/watch?v=Kz6p2N4bBns; Maths Genie - Negative and Fractional Powers Explained: https://www.youtube.com/watch?v=F3g81hGfM_U</t>
+  </si>
+  <si>
+    <t>BBC Bitesize - Powers and Roots (includes exponents and indices): https://www.bbc.co.uk/bitesize/guides/zpcxpv4/revision/1; Maths Is Fun - Exponents Introduction and Examples: https://www.mathsisfun.com/exponent.html; Paul's Online Math Notes - Integer Exponents (detailed explanations and examples): https://tutorial.math.lamar.edu/Classes/Alg/IntegerExponents.aspx; LibreTexts - Properties of Exponents (open textbook chapter): https://math.libretexts.org/Bookshelves/Algebra/Elementary_Algebra_2e_(OpenStax)/01:_Foundations/1.03:_Properties_of_Exponents; CK-12 Foundation - Exponents (textbook content with worked examples): https://www.ck12.org/algebra/exponents-algebra/lesson/Exponents-Alg-I/</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of square roots and cube roots; Familiarity with prime factorization; Knowledge of rational and irrational numbers.</t>
+  </si>
+  <si>
+    <t>Definition and identification of surds; Simplification of surds; Addition and subtraction of surds; Multiplication and division of surds; Rationalizing the denominator (single term); Rationalizing the denominator (binomial surds using conjugates); Solving equations involving surds; Properties of surds.</t>
+  </si>
+  <si>
+    <t>Surd Simplifier: A Python program that takes an integer and returns its simplified surd form (e.g., input 72, output 6√2); Rationalize Denominator Calculator: A script that takes a fraction with a surd in the denominator and rationalizes it; Surd Expression Evaluator: Develop a tool to evaluate basic arithmetic expressions involving surds (e.g., (2√3 + 5√2)(√3 - √2)); Random Surd Problem Generator: Create a program to generate random surd simplification or rationalization problems for practice; Surd Equation Solver: A basic script to solve simple linear equations involving surds, showing step-by-step solutions.</t>
+  </si>
+  <si>
+    <t>Surd Dominoes: Create a set of dominoes where one half has a surd expression and the other has its simplified form or an equivalent expression; Rationalization Card Sort: Design cards with surd fractions and their corresponding rationalized forms for matching exercises; Surd Properties Mind Map: Develop a comprehensive visual mind map illustrating all properties, operations, and rules for surds; Real-World Surds Application Report: Research and present on real-world scenarios where irrational numbers or surds are inherently used, such as in construction, architecture (diagonal lengths), or musical scales; Surd Crossword Puzzle: Construct a crossword puzzle where answers are simplified surds or terms related to surds.</t>
+  </si>
+  <si>
+    <t>Khan Academy Surds Practice: https://www.khanacademy.org/math/algebra/x2f8bb11595b61c86:rational-exponents-radicals/x2f8bb11595b61c86:simplify-radical-expressions/e/simplify-radical-expressions-2; Corbettmaths Surds Worksheets (various levels): https://corbettmaths.com/contents/ (search for 'Surds'); Maths Genie GCSE Surds Quizzes: https://www.mathsgenie.co.uk/gcse.html (under 'Number', find 'Surds'); BBC Bitesize Surds Revision and Quizzes: https://www.bbc.co.uk/bitesize/guides/zpc4sg8/revision/1; DrFrostMaths Surds Practice (requires login, extensive question bank): https://www.drfrostmaths.com/ (search for 'Surds').</t>
+  </si>
+  <si>
+    <t>Khan Academy: Simplifying Square Roots (Introduction to Surds): https://www.youtube.com/watch?v=k3B7W53T-oQ; GCSE Maths - Surds Introduction and Simplifying Surds - HegartyMaths: https://www.youtube.com/watch?v=yYJ6XpG8230; Addition and Subtraction of Surds - Maths Made Easy: https://www.youtube.com/watch?v=XWpT58-xM8w; Multiplication and Division of Surds - GCSE Maths Tutor: https://www.youtube.com/watch?v=nE-kU4v596E; Rationalizing the Denominator (Single and Double Surds) - ExamSolutions: https://www.youtube.com/watch?v=cM2yS-s4j5Y.</t>
+  </si>
+  <si>
+    <t>BBC Bitesize - Surds Explanation and Examples: https://www.bbc.co.uk/bitesize/guides/zpc4sg8/revision/1; Maths is Fun - Surds Comprehensive Guide: https://www.mathsisfun.com/surds.html; S-cool! GCSE Maths Revision - What are Surds: https://www.s-cool.co.uk/gcse/maths/surds/revise-it/what-are-surds; Corbettmaths Textbook Exercises (PDFs available for download): https://corbettmaths.com/wp-content/uploads/2018/09/Surds-pdf.pdf; 'GCSE Maths Edexcel Higher Student Book' (e.g., by Pearson or Hodder Education) - Chapter on Surds.</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of repeated multiplication.</t>
+  </si>
+  <si>
+    <t>Definition of an exponent (base and power); Positive integer exponents; Zero exponent rule (a^0 = 1); Negative integer exponents (a^-n = 1/a^n); Fractional exponents (rational exponents, a^(m/n) = nth_root(a^m)); Laws of exponents (product rule, quotient rule, power rule); Power of a product/quotient rule; Scientific notation; Solving basic exponential equations; Understanding very large and very small numbers.</t>
+  </si>
+  <si>
+    <t>Exponent Calculator: A program that takes a base and an exponent (integer or rational) and calculates the result; Laws of Exponents Game: A simple quiz game where users must identify the correct law of exponents for a given expression; Scientific Notation Converter: A script that converts numbers to and from scientific notation; Exponential Growth/Decay Simulator: A program to model simple exponential growth or decay scenarios, e.g., compound interest or radioactive decay; Solving Basic Exponential Equations: A tool to find 'x' in simple equations like a^x = b or a^(bx) = c, showing intermediate steps.</t>
+  </si>
+  <si>
+    <t>Exponent Rule Flashcards: Create a complete set of flashcards for each law of exponents, with the rule on one side and examples on the other; Powers of 2/3/10 Chart: Design a visual chart illustrating the first 10-15 powers of common bases (e.g., 2, 3, 5, 10); Exponent Maze: A worksheet where students navigate a maze by correctly applying exponent rules to move from one step to the next; Scientific Notation Real-World Examples Poster: Create an informative poster illustrating real-world applications of scientific notation in fields like astronomy, chemistry, or computing; Exponent Board Game: Design a board game where players advance by solving exponent problems and applying rules correctly.</t>
+  </si>
+  <si>
+    <t>Khan Academy Exponents Practice: https://www.khanacademy.org/math/algebra/x2f8bb11595b61c86:rational-exponents-radicals/x2f8bb11595b61c86:exponent-properties-review/e/properties-of-exponents; IXL Exponents Practice (various grades): https://www.ixl.com/math/grade-8/evaluate-expressions-using-properties-of-exponents; Brilliant.org Exponents Course (first few lessons free): https://brilliant.org/courses/exponents/; Math Playground Exponent Games and Activities: https://www.mathplayground.com/grade_6_games.html (search for 'exponents'); Quia Exponents Quizzes and Games: https://www.quia.com/jg/320023.html.</t>
+  </si>
+  <si>
+    <t>Khan Academy: Intro to Exponents - Understanding Powers: https://www.youtube.com/watch?v=JdCIrD-y7ML; Laws of Exponents (Indices) - Don't Memorise: https://www.youtube.com/watch?v=gT8y6I4C204; Zero and Negative Exponents - Math Antics: https://www.youtube.com/watch?v=DM3lS4h_vM4; Fractional Exponents (Rational Exponents) Explained - The Organic Chemistry Tutor: https://www.youtube.com/watch?v=P2b8T1m92-k; Scientific Notation Explained - Professor Dave Explains: https://www.youtube.com/watch?v=CqHj79T5M1Y.</t>
+  </si>
+  <si>
+    <t>BBC Bitesize - Powers and Roots (Exponents/Indices) Explanation: https://www.bbc.co.uk/bitesize/guides/zc6p3k7/revision/1; Maths is Fun - Exponents: https://www.mathsisfun.com/exponent.html; S-cool! GCSE Maths Revision - Indices: https://www.s-cool.co.uk/gcse/maths/indices; Corbettmaths Textbook Exercises (PDFs available for download): https://corbettmaths.com/wp-content/uploads/2018/09/Indices-pdf.pdf; 'Pre-Algebra' or 'Algebra 1' Textbooks (e.g., OpenStax, Larson, McDougal Littell) - Dedicated Chapters on Exponents and their properties.</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of square roots and cube roots; Familiarity with prime factorization; Basic algebraic manipulation; Understanding of rational and irrational numbers.</t>
+  </si>
+  <si>
+    <t>Definition and identification of surds; Simplification of surds (e.g., √12 = 2√3); Addition and subtraction of surds with common surd parts; Multiplication of surds, including binomial products; Division of surds and rationalizing the denominator for single terms; Rationalizing the denominator for binomial terms using conjugate pairs; Solving simple equations involving surds by squaring both sides; Application of surds in geometry problems (e.g., Pythagoras theorem); Understanding the properties of square roots and nth roots.</t>
+  </si>
+  <si>
+    <t>Python script to simplify surds: User inputs a number, script outputs its simplified surd form (e.g., input 75, output 5√3); JavaScript calculator for surd operations: A web-based calculator that performs addition, subtraction, multiplication, and division of surds; C++ program to rationalize denominators: Takes a surd expression (e.g., 1/(√2+1)) as input and outputs the rationalized form; Java application to identify perfect squares/cubes: Determines if a given number's root is a surd or a rational number; MATLAB script for surd-based area/perimeter calculations: Calculates areas or perimeters of geometric figures where side lengths are expressed as surds.</t>
+  </si>
+  <si>
+    <t>Create a detailed poster explaining all surd simplification rules with multiple worked examples; Develop a set of flashcards for common surd forms, their simplified versions, and conjugate pairs; Design a board game where players solve surd problems to advance spaces, including rationalization challenges; Write an essay or detailed report on the historical context and practical applications of surds in fields like engineering or architecture; Prepare a presentation illustrating the step-by-step process of solving complex surd equations, highlighting common pitfalls.</t>
+  </si>
+  <si>
+    <t>Khan Academy: Simplifying square roots problems with step-by-step solutions; BBC Bitesize: GCSE Maths Surds practice questions across various difficulty levels; Corbettmaths: Extensive collection of surds worksheets and fully worked solutions; DrFrostMaths: Online problem generator specifically for surds, allowing customisation of question types; IXL Maths: Interactive exercises for simplifying radical expressions and rationalizing denominators.</t>
+  </si>
+  <si>
+    <t>Simplifying Surds - ExamSolutions: https://www.youtube.com/watch?v=gT8YfPjP1uM; Adding and Subtracting Surds - Math Antics: https://www.youtube.com/watch?v=3-EwLh6P48E; Multiplying and Dividing Surds - Organic Chemistry Tutor: https://www.youtube.com/watch?v=KkYm3W2kFq0; Rationalizing the Denominator (Surds) - HegartyMaths: https://www.youtube.com/watch?v=R2j9jQ4M-fM; Solving Surd Equations - patrickJMT: https://www.youtube.com/watch?v=9L-h8UjX7w0.</t>
+  </si>
+  <si>
+    <t>Pure Mathematics 1 (P1) Textbook - Comprehensive chapter on Surds with examples and exercises (e.g., Cambridge, Oxford International AS &amp; A Level): https://www.amazon.com/Pure-Mathematics-1-International-AS/dp/1107567794; GCSE Maths Higher Level Textbook - Dedicated section on Surds for UK curriculum (e.g., Collins GCSE Maths): https://www.amazon.co.uk/Collins-GCSE-Maths-Higher-Student/dp/0007530272; Corbettmaths.com - Detailed notes, examples, and practice questions for Surds: https://corbettmaths.com/2013/05/29/surds/; Maths is Fun - Easy-to-understand introduction to Surds with interactive examples: https://www.mathsisfun.com/surds.html; Bitesize GCSE Maths - In-depth revision guide for Surds with key facts and quiz questions: https://www.bbc.co.uk/bitesize/guides/zpcxpv4/revision/1.</t>
+  </si>
+  <si>
+    <t>Basic arithmetic operations (addition, subtraction, multiplication, division); Understanding of integers and rational numbers; Familiarity with multiplication as repeated addition; Basic algebraic notation; Knowledge of order of operations (PEMDAS/BODMAS).</t>
+  </si>
+  <si>
+    <t>Definition and notation of exponents (base, power/index); Laws of exponents for multiplication (a^m * a^n = a^(m+n)); Laws of exponents for division (a^m / a^n = a^(m-n)); Power of a power law ((a^m)^n = a^(mn)); Zero exponent rule (a^0 = 1); Negative exponents (a^(-n) = 1/a^n); Fractional exponents and their relation to roots (a^(m/n) = nth_root(a^m)); Scientific notation for very large and small numbers; Solving basic exponential equations; Real-world applications of exponents (e.g., compound interest, population growth, radioactive decay).</t>
+  </si>
+  <si>
+    <t>Python program to calculate powers: User inputs base and exponent, program outputs the result, handling positive, negative, and zero exponents; C# console application for scientific notation converter: Converts any decimal number to and from scientific notation; Java GUI application to demonstrate exponent laws: Allows users to input expressions and see the simplified result based on chosen exponent rules; JavaScript calculator for compound interest: Calculates final amount, interest earned, or time required using exponential formulas; MATLAB script for modeling exponential growth/decay: Visualizes population growth, compound interest, or radioactive decay over a specified period.</t>
+  </si>
+  <si>
+    <t>Create a comprehensive poster illustrating all the laws of exponents with clear, color-coded examples; Develop a trivia game based on solving exponential expressions and identifying correct exponent laws; Write a detailed report on the historical development of exponential notation and its crucial impact on scientific and mathematical fields; Design a visual aid (e.g., an infographic) to clearly explain the concepts of negative and fractional exponents; Prepare a presentation on the diverse real-world applications of exponents in finance, biology, and computer science.</t>
+  </si>
+  <si>
+    <t>Khan Academy: Extensive practice problems on exponent properties, including negative and fractional exponents; IXL Maths: Interactive exercises for evaluating expressions using properties of exponents and solving exponential equations; Corbettmaths: Indices worksheets and practice questions with detailed solutions covering all exponent laws; DrFrostMaths: Online problem generator for exponent laws, allowing for varied difficulty and topic focus; Math-Drills.com: Printable worksheets for exponents, covering basic calculations, laws, and scientific notation.</t>
+  </si>
+  <si>
+    <t>Introduction to Exponents - Math Antics: https://www.youtube.com/watch?v=Zf_xV1I8J9g; Laws of Exponents - The Organic Chemistry Tutor: https://www.youtube.com/watch?v=g5cO0d4L1y4; Negative Exponents Explained - Khan Academy: https://www.youtube.com/watch?v=DM3lY2yGqG0; Fractional Exponents - PatrickJMT: https://www.youtube.com/watch?v=Ld_L1p0142A; Scientific Notation - Professor Dave Explains: https://www.youtube.com/watch?v=i9Y1V5P8C24.</t>
+  </si>
+  <si>
+    <t>Algebra 1 Textbook - Comprehensive chapter on Exponents, covering laws and basic applications (various publishers); Intermediate Algebra Textbook - Dedicated section on Exponents and Radicals, linking to roots (e.g., Blitzer, Bittinger): https://www.amazon.com/Intermediate-Algebra-Concepts-Applications-Edition/dp/0321785536; Maths is Fun - Clear and concise explanation of Exponents and Powers: https://www.mathsisfun.com/exponent.html; Bitesize GCSE Maths - In-depth revision guide for Indices (Exponents) with key facts and practice questions: https://www.bbc.co.uk/bitesize/guides/z889jxs/revision/1; Brilliant.org - Exponents fundamentals, offering interactive lessons and challenges: https://brilliant.org/wiki/exponents-fundamentals/.</t>
   </si>
 </sst>
 </file>
@@ -213,16 +264,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:G7" totalsRowShown="0">
-  <autoFilter ref="A1:G7"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H9" totalsRowShown="0">
+  <autoFilter ref="A1:H9"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="topic" dataDxfId="0"/>
     <tableColumn id="2" name="prerequisites" dataDxfId="0"/>
     <tableColumn id="3" name="sub_topics" dataDxfId="0"/>
     <tableColumn id="4" name="coding_projects" dataDxfId="0"/>
     <tableColumn id="5" name="non_coding_projects" dataDxfId="0"/>
-    <tableColumn id="6" name="video_resources" dataDxfId="0"/>
-    <tableColumn id="7" name="text_resources" dataDxfId="0"/>
+    <tableColumn id="6" name="online_problem_sets" dataDxfId="0"/>
+    <tableColumn id="7" name="video_resources" dataDxfId="0"/>
+    <tableColumn id="8" name="text_resources" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -513,10 +565,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -538,143 +590,216 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>41</v>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>48</v>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
